--- a/DSA_Level1_Tracker.xlsx
+++ b/DSA_Level1_Tracker.xlsx
@@ -634,18 +634,26 @@
           <t>6</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Number Theory I. Problems + operator drills set in Day02/. Difficulty nudged up (Day1 71/100 ADVANCE). Required: prime O(sqrt n), digit-loop for Armstrong/palindrome. Carryover: fix Day1 Q4 (O(n) one-pass) &amp; Q10 (real power-of-two).</t>
+          <t>Day2 ~91/100 LEVEL UP. 10/10 core PASS incl edges; stretch Q11/Q12 skipped. Strong: O(sqrt n) prime, math digit loops, bit-trick power-of-two (fixes Day1 Q10). Nits: redundant ==True / ternary-of-bool, float sqrt risk in is_prime. Difficulty bumped aggressively for Day3.</t>
         </is>
       </c>
     </row>
@@ -663,24 +671,28 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Number Theory II (GCD/LCM/Fibonacci)</t>
+          <t>Arrays + Hashing/Dict (+ NT II warm-up: GCD/LCM/Fib)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Pulled forward arrays + dictionaries per request (level-up). 12 Qs: GCD/LCM/Fib, one-pass max/min (Day1 Q4 fix), second largest, move zeros, missing number, rotate; dict freq, two-sum, first non-repeating, anagram, majority. Required O(n) / O(1) space where stated.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">

--- a/DSA_Level1_Tracker.xlsx
+++ b/DSA_Level1_Tracker.xlsx
@@ -708,12 +708,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Pattern Printing</t>
+          <t>Strings I + Search &amp; Two Pointers</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -725,7 +725,11 @@
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Set up assuming Day3 ~50 -&gt; ADVANCE (one notch up). 12 Qs: string fundamentals (reverse, palindrome, vowels, words, toggle, dedup, first-unique) + linear &amp; binary search (O(log n)) and two-pointer pair-sum. Playground has self-check harness.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">

--- a/DSA_Level1_Tracker.xlsx
+++ b/DSA_Level1_Tracker.xlsx
@@ -745,12 +745,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Arrays I</t>
+          <t>Sorting (Basics + Applications)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -762,7 +762,11 @@
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>12 Qs: implement bubble/selection/insertion by hand + is_sorted; applications: sort 0/1/2, merge sorted (two pointers), kth smallest/largest, find duplicates, sort by frequency; stretch merge sort + quick sort. Complexity table in problems.md. Playground self-checks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">

--- a/DSA_Level1_Tracker.xlsx
+++ b/DSA_Level1_Tracker.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -690,7 +690,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Pulled forward arrays + dictionaries per request (level-up). 12 Qs: GCD/LCM/Fib, one-pass max/min (Day1 Q4 fix), second largest, move zeros, missing number, rotate; dict freq, two-sum, first non-repeating, anagram, majority. Required O(n) / O(1) space where stated.</t>
+          <t>Pulled forward arrays + dictionaries per request (level-up). 12 Qs: GCD/LCM/Fib, one-pass max/min (Day1 Q4 fix), second largest, move zeros, missing number, rotate; dict freq, two-sum, first non-repeating, anagram, majority. Required O(n) / O(1) space where stated. [RECOVERY: schedule re-baselined to start 2026-06-29 after Day4/5 were deferred. See RECOVERY_PLAN.md. Finish Day3 Q7-Q12 first.]</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -873,7 +873,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -972,7 +972,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">

--- a/DSA_Level1_Tracker.xlsx
+++ b/DSA_Level1_Tracker.xlsx
@@ -679,18 +679,22 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Pulled forward arrays + dictionaries per request (level-up). 12 Qs: GCD/LCM/Fib, one-pass max/min (Day1 Q4 fix), second largest, move zeros, missing number, rotate; dict freq, two-sum, first non-repeating, anagram, majority. Required O(n) / O(1) space where stated. [RECOVERY: schedule re-baselined to start 2026-06-29 after Day4/5 were deferred. See RECOVERY_PLAN.md. Finish Day3 Q7-Q12 first.]</t>
+          <t>Review #1: ~74/100 ADVANCE (almost level-up). 13/15 harness-green; 12 truly correct. FIX: Q9 rotate broken (k%=len needed, slice/remove logic wrong - passed case1 by coincidence); Q13 is_anagram not attempted; Q11 two_sum passes tests by luck but only checks ADJACENT pairs (will IndexError/miss on non-adjacent) - use hashing. Nits: Q7 uses 0. (float); Q6 sorted() not one-pass. Strong: digit/two-pointer/hashing/sliding-window all solid. Review cap 1/5.</t>
         </is>
       </c>
     </row>
@@ -782,12 +786,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Arrays II (search/duplicates/rotate)</t>
+          <t>Recursion (base/recursive case + classics)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -799,7 +803,11 @@
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>12 Qs: sum_to_n, fib, sum_digits, power, naturals, reverse string, gcd, array sum, palindrome, recursive binary search; stretch fast_power O(log n) + tower of hanoi. Focus: base case + shrinking input + call-stack space. Playground self-checks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
